--- a/resources/UserDetails_prod.xlsx
+++ b/resources/UserDetails_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Email</t>
   </si>
@@ -36,6 +36,63 @@
   </si>
   <si>
     <t>HarlandKonopelskiJr@yopmail.com</t>
+  </si>
+  <si>
+    <t>CassyLubowitz@yopmail.com</t>
+  </si>
+  <si>
+    <t>EugeneReichelPhD@yopmail.com</t>
+  </si>
+  <si>
+    <t>RayFlatley@yopmail.com</t>
+  </si>
+  <si>
+    <t>JcLangworth@yopmail.com</t>
+  </si>
+  <si>
+    <t>SalleyWuckertJr@yopmail.com</t>
+  </si>
+  <si>
+    <t>MrsKathaleenPrice@yopmail.com</t>
+  </si>
+  <si>
+    <t>WilfordRutherford@yopmail.com</t>
+  </si>
+  <si>
+    <t>SammieSmitham@yopmail.com</t>
+  </si>
+  <si>
+    <t>ZoraidaAnderson@yopmail.com</t>
+  </si>
+  <si>
+    <t>FredericHoweDDS@yopmail.com</t>
+  </si>
+  <si>
+    <t>ToryMcCullough@yopmail.com</t>
+  </si>
+  <si>
+    <t>MatthewLind@yopmail.com</t>
+  </si>
+  <si>
+    <t>NylaMarvinMD@yopmail.com</t>
+  </si>
+  <si>
+    <t>AngeleKilbackMD@yopmail.com</t>
+  </si>
+  <si>
+    <t>PeteOlson@yopmail.com</t>
+  </si>
+  <si>
+    <t>LynnGoyetteSr@yopmail.com</t>
+  </si>
+  <si>
+    <t>LornaWuckert@yopmail.com</t>
+  </si>
+  <si>
+    <t>BennyDickens@yopmail.com</t>
+  </si>
+  <si>
+    <t>RustyHickle@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1195,7 +1252,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1213,6 +1270,101 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/UserDetails_prod.xlsx
+++ b/resources/UserDetails_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Email</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>RustyHickle@yopmail.com</t>
+  </si>
+  <si>
+    <t>EldonTrantow@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1252,7 +1255,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1365,6 +1368,11 @@
         <v>21</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
